--- a/campus-placement/qa/C-1-Role-Based-Screen-Access.xlsx
+++ b/campus-placement/qa/C-1-Role-Based-Screen-Access.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-1 Manual Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -27,11 +28,9 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -54,16 +53,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -427,7 +423,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M261"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -440,7 +436,8 @@
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="13"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,7 +507,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>C1-VISIT-001</t>
@@ -546,14 +543,14 @@
           <t>/dashboard/alerts</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Login with demo account
 Navigate to /dashboard/alerts
 Wait for page to load completely</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Target screen opens successfully
 No runtime error banner/toast/modal is shown
@@ -567,17 +564,13 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/alerts</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="111" customHeight="1">
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>C1-VISIT-002</t>
@@ -613,14 +606,14 @@
           <t>/dashboard/feedback</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Login with demo account
 Navigate to /dashboard/feedback
 Wait for page to load completely</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Target screen opens successfully
 No runtime error banner/toast/modal is shown
@@ -634,18 +627,11 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/feedback", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -704,15 +690,11 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/my-exports</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -771,15 +753,11 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/student/applications</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -838,18 +816,11 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/calendar", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -908,15 +879,11 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/student/clarifications</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -975,15 +942,11 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/student/discussions</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1042,18 +1005,11 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/documents", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1112,18 +1068,11 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1182,18 +1131,11 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/internships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1252,18 +1194,11 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/interviews", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1322,18 +1257,11 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1392,15 +1320,11 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/student/overview</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1459,18 +1383,11 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/profile", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1529,15 +1446,11 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/student/projects</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1595,18 +1508,11 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/audit-reports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1664,18 +1570,11 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/colleges", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1733,15 +1632,11 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/admin/employers</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1799,15 +1694,11 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/admin/feedback</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1865,18 +1756,11 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1934,18 +1818,11 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/pending-registrations", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2003,18 +1880,11 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/settings", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2072,18 +1942,11 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/users", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2141,18 +2004,11 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n"/>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/applications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2210,15 +2066,11 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/audit-reports</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2276,15 +2128,11 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/calendar</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2342,18 +2190,11 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/clarifications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2411,18 +2252,11 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/discussions", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2480,18 +2314,11 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2549,18 +2376,11 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/employers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2618,15 +2438,11 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/employers/requests</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2684,18 +2500,11 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/enrollment-key", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2753,15 +2562,11 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/events</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2819,15 +2624,11 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/guest-engagements</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2885,15 +2686,11 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/hiring-assessment</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2951,18 +2748,11 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/infrastructure", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3020,18 +2810,11 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/internship-results", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3089,18 +2872,11 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/internships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3158,18 +2934,11 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/interviews", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3227,18 +2996,11 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3296,15 +3058,11 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/offers-upload</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3362,18 +3120,11 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3431,18 +3182,11 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/reports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3500,18 +3244,11 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/rules", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3569,18 +3306,11 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/settings", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3638,18 +3368,11 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/sponsorships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3707,18 +3430,11 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/students", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3776,18 +3492,11 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n"/>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/applications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3845,18 +3554,11 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n"/>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/assessment-summary", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3914,18 +3616,11 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n"/>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/assessment-uploads", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3983,15 +3678,11 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/employer/calendar</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4049,15 +3740,11 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/employer/campus-guest-needs</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4115,15 +3802,11 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/employer/discussions</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4181,15 +3864,11 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n"/>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/employer/drives</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4247,15 +3926,11 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/employer/hiring-assessment</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4313,15 +3988,11 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/employer/internships</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4379,15 +4050,11 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/employer/interviews</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4445,18 +4112,11 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n"/>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/jobs", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4514,18 +4174,11 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n"/>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4583,18 +4236,11 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n"/>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/offers-upload", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4652,18 +4298,11 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n"/>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4721,18 +4360,11 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/profile", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4790,18 +4422,11 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n"/>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/projects", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4859,15 +4484,11 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n"/>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/employer/select-campus</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4925,15 +4546,11 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n"/>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/employer/sponsorships</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4992,18 +4609,11 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n"/>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/alerts", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5062,18 +4672,11 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n"/>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/applications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5132,15 +4735,11 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n"/>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/employer/assessment-summary</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5199,15 +4798,11 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n"/>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/employer/assessment-uploads</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5266,18 +4861,11 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n"/>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/calendar", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5336,18 +4924,11 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n"/>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/campus-guest-needs", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5406,18 +4987,11 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n"/>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/discussions", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5476,18 +5050,11 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n"/>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5546,18 +5113,11 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n"/>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/hiring-assessment", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5616,15 +5176,11 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n"/>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/employer/internships</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5683,15 +5239,11 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n"/>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>Failed to load /dashboard/employer/interviews (URL: http://localhost:3000/dashboard/employer/select-campus)</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5750,18 +5302,11 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n"/>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/jobs", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5820,15 +5365,11 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n"/>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/employer/offers</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5887,18 +5428,11 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n"/>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/offers-upload", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5957,18 +5491,11 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n"/>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6027,18 +5554,11 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n"/>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/profile", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6097,18 +5617,11 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n"/>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/projects", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6167,15 +5680,11 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n"/>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/employer/select-campus</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -6234,18 +5743,11 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n"/>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/sponsorships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6304,18 +5806,11 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n"/>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/feedback", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6374,18 +5869,11 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n"/>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/my-exports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6443,18 +5931,11 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n"/>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/audit-reports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -6512,18 +5993,11 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n"/>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/colleges", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6581,18 +6055,11 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n"/>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/employers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6650,18 +6117,11 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n"/>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/feedback", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6719,18 +6179,11 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n"/>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6788,18 +6241,11 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n"/>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/pending-registrations", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6857,18 +6303,11 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n"/>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/settings", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6926,18 +6365,11 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n"/>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/users", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6995,18 +6427,11 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n"/>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/applications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -7064,18 +6489,11 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n"/>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/audit-reports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -7133,18 +6551,11 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n"/>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/calendar", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -7202,18 +6613,11 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n"/>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/clarifications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7271,18 +6675,11 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="n"/>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/discussions", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -7340,18 +6737,11 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n"/>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7409,15 +6799,11 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n"/>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/employers</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -7475,15 +6861,11 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="n"/>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/employers/requests</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -7541,18 +6923,11 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n"/>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/enrollment-key", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7610,15 +6985,11 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="n"/>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/events</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7676,18 +7047,11 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n"/>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/guest-engagements", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -7745,18 +7109,11 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n"/>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/hiring-assessment", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7814,18 +7171,11 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="n"/>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/infrastructure", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7883,18 +7233,11 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n"/>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/internship-results", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7952,15 +7295,11 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="n"/>
-      <c r="M110" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/internships</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -8018,18 +7357,11 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n"/>
-      <c r="M111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/interviews", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -8087,18 +7419,11 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n"/>
-      <c r="M112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -8156,15 +7481,11 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="n"/>
-      <c r="M113" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/offers-upload</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -8222,15 +7543,11 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="n"/>
-      <c r="M114" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/overview</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -8288,18 +7605,11 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="n"/>
-      <c r="M115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/reports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -8357,18 +7667,11 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n"/>
-      <c r="M116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/rules", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -8426,18 +7729,11 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="n"/>
-      <c r="M117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/settings", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -8495,15 +7791,11 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n"/>
-      <c r="M118" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/sponsorships</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -8561,18 +7853,11 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="n"/>
-      <c r="M119" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/students", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -8630,15 +7915,11 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n"/>
-      <c r="M120" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/student/applications</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -8696,18 +7977,11 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n"/>
-      <c r="M121" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/calendar", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -8765,15 +8039,11 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n"/>
-      <c r="M122" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/student/clarifications</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -8831,18 +8101,11 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n"/>
-      <c r="M123" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/discussions", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -8900,18 +8163,11 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="n"/>
-      <c r="M124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/documents", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -8969,18 +8225,11 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n"/>
-      <c r="M125" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -9038,18 +8287,11 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n"/>
-      <c r="M126" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/internships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -9107,18 +8349,11 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n"/>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/interviews", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -9176,18 +8411,11 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="n"/>
-      <c r="M128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -9245,18 +8473,11 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="n"/>
-      <c r="M129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -9314,18 +8535,11 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="n"/>
-      <c r="M130" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/profile", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -9383,18 +8597,11 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="n"/>
-      <c r="M131" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/projects", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -9453,18 +8660,11 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="n"/>
-      <c r="M132" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/alerts", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -9523,18 +8723,11 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="n"/>
-      <c r="M133" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/applications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -9593,18 +8786,11 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="n"/>
-      <c r="M134" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/audit-reports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -9663,18 +8849,11 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="n"/>
-      <c r="M135" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/calendar", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -9733,18 +8912,11 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="n"/>
-      <c r="M136" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/clarifications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -9803,18 +8975,11 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="n"/>
-      <c r="M137" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/discussions", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -9873,18 +9038,11 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n"/>
-      <c r="M138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -9943,18 +9101,11 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n"/>
-      <c r="M139" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/employers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -10013,18 +9164,11 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="n"/>
-      <c r="M140" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/employers/requests", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -10083,18 +9227,11 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n"/>
-      <c r="M141" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/enrollment-key", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -10153,18 +9290,11 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="n"/>
-      <c r="M142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/events", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -10223,18 +9353,11 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="n"/>
-      <c r="M143" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/guest-engagements", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -10293,18 +9416,11 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L144" s="2" t="n"/>
-      <c r="M144" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/hiring-assessment", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -10363,18 +9479,11 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="n"/>
-      <c r="M145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/infrastructure", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -10433,18 +9542,11 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L146" s="2" t="n"/>
-      <c r="M146" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/internship-results", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -10503,18 +9605,11 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="n"/>
-      <c r="M147" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/internships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -10573,18 +9668,11 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="n"/>
-      <c r="M148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/interviews", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -10643,18 +9731,11 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n"/>
-      <c r="M149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -10713,18 +9794,11 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L150" s="2" t="n"/>
-      <c r="M150" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/offers-upload", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -10783,18 +9857,11 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="n"/>
-      <c r="M151" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -10853,18 +9920,11 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="n"/>
-      <c r="M152" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/reports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -10923,18 +9983,11 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="n"/>
-      <c r="M153" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/rules", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -10993,18 +10046,11 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="n"/>
-      <c r="M154" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/settings", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -11063,18 +10109,11 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="n"/>
-      <c r="M155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/sponsorships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -11133,18 +10172,11 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="n"/>
-      <c r="M156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/students", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -11203,18 +10235,11 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="n"/>
-      <c r="M157" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/feedback", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -11273,18 +10298,11 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="n"/>
-      <c r="M158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/my-exports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -11342,18 +10360,11 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n"/>
-      <c r="M159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/audit-reports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -11411,18 +10422,11 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="n"/>
-      <c r="M160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/colleges", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -11480,18 +10484,11 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="n"/>
-      <c r="M161" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/employers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -11549,18 +10546,11 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="n"/>
-      <c r="M162" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/feedback", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -11618,18 +10608,11 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="n"/>
-      <c r="M163" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -11687,18 +10670,11 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="n"/>
-      <c r="M164" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/pending-registrations", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -11756,18 +10732,11 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="n"/>
-      <c r="M165" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/settings", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -11825,18 +10794,11 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="n"/>
-      <c r="M166" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/users", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -11894,18 +10856,11 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="n"/>
-      <c r="M167" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/applications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -11963,18 +10918,11 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="n"/>
-      <c r="M168" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/assessment-summary", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -12032,18 +10980,11 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="n"/>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/assessment-uploads", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -12101,18 +11042,11 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L170" s="2" t="n"/>
-      <c r="M170" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/calendar", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -12170,18 +11104,11 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="n"/>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/campus-guest-needs", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -12239,18 +11166,11 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L172" s="2" t="n"/>
-      <c r="M172" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/discussions", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -12308,18 +11228,11 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="n"/>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr"/>
+      <c r="M173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -12377,18 +11290,11 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L174" s="2" t="n"/>
-      <c r="M174" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/hiring-assessment", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr"/>
+      <c r="M174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -12446,18 +11352,11 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="n"/>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/internships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -12515,18 +11414,11 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L176" s="2" t="n"/>
-      <c r="M176" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/interviews", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -12584,18 +11476,11 @@
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L177" s="2" t="n"/>
-      <c r="M177" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/jobs", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -12653,18 +11538,11 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L178" s="2" t="n"/>
-      <c r="M178" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -12722,18 +11600,11 @@
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L179" s="2" t="n"/>
-      <c r="M179" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/offers-upload", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr"/>
+      <c r="M179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -12791,18 +11662,11 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L180" s="2" t="n"/>
-      <c r="M180" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -12860,18 +11724,11 @@
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L181" s="2" t="n"/>
-      <c r="M181" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/profile", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr"/>
+      <c r="M181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -12929,18 +11786,11 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L182" s="2" t="n"/>
-      <c r="M182" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/projects", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -12998,18 +11848,11 @@
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L183" s="2" t="n"/>
-      <c r="M183" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/select-campus", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr"/>
+      <c r="M183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -13067,18 +11910,11 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L184" s="2" t="n"/>
-      <c r="M184" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/sponsorships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr"/>
+      <c r="M184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -13136,18 +11972,11 @@
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L185" s="2" t="n"/>
-      <c r="M185" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/applications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr"/>
+      <c r="M185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -13205,18 +12034,11 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="n"/>
-      <c r="M186" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/calendar", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -13274,18 +12096,11 @@
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="n"/>
-      <c r="M187" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/clarifications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr"/>
+      <c r="M187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -13343,18 +12158,11 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L188" s="2" t="n"/>
-      <c r="M188" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/discussions", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -13412,18 +12220,11 @@
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L189" s="2" t="n"/>
-      <c r="M189" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/documents", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr"/>
+      <c r="M189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -13481,18 +12282,11 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L190" s="2" t="n"/>
-      <c r="M190" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr"/>
+      <c r="M190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -13550,18 +12344,11 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L191" s="2" t="n"/>
-      <c r="M191" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/internships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr"/>
+      <c r="M191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -13619,18 +12406,11 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L192" s="2" t="n"/>
-      <c r="M192" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/interviews", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr"/>
+      <c r="M192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -13688,18 +12468,11 @@
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L193" s="2" t="n"/>
-      <c r="M193" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr"/>
+      <c r="M193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -13757,18 +12530,11 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L194" s="2" t="n"/>
-      <c r="M194" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="inlineStr"/>
+      <c r="M194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -13826,18 +12592,11 @@
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L195" s="2" t="n"/>
-      <c r="M195" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/profile", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr"/>
+      <c r="M195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -13895,18 +12654,11 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L196" s="2" t="n"/>
-      <c r="M196" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/projects", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L196" s="2" t="inlineStr"/>
+      <c r="M196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -13965,15 +12717,11 @@
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="L197" s="2" t="n"/>
-      <c r="M197" s="2" t="inlineStr">
-        <is>
-          <t>Successfully loaded /dashboard/admin/audit-reports</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr"/>
+      <c r="M197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -14032,18 +12780,11 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L198" s="2" t="n"/>
-      <c r="M198" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/colleges", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr"/>
+      <c r="M198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -14102,18 +12843,11 @@
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L199" s="2" t="n"/>
-      <c r="M199" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/employers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr"/>
+      <c r="M199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -14172,18 +12906,11 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L200" s="2" t="n"/>
-      <c r="M200" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/feedback", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr"/>
+      <c r="M200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -14242,18 +12969,11 @@
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L201" s="2" t="n"/>
-      <c r="M201" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr"/>
+      <c r="M201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -14312,18 +13032,11 @@
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L202" s="2" t="n"/>
-      <c r="M202" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/pending-registrations", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L202" s="2" t="inlineStr"/>
+      <c r="M202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -14382,18 +13095,11 @@
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L203" s="2" t="n"/>
-      <c r="M203" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/settings", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="inlineStr"/>
+      <c r="M203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -14452,18 +13158,11 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L204" s="2" t="n"/>
-      <c r="M204" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/admin/users", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L204" s="2" t="inlineStr"/>
+      <c r="M204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -14522,18 +13221,11 @@
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L205" s="2" t="n"/>
-      <c r="M205" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/my-exports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L205" s="2" t="inlineStr"/>
+      <c r="M205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -14591,18 +13283,11 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L206" s="2" t="n"/>
-      <c r="M206" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/alerts", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr"/>
+      <c r="M206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -14660,18 +13345,11 @@
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L207" s="2" t="n"/>
-      <c r="M207" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/applications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L207" s="2" t="inlineStr"/>
+      <c r="M207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -14729,18 +13407,11 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L208" s="2" t="n"/>
-      <c r="M208" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/audit-reports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr"/>
+      <c r="M208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -14798,18 +13469,11 @@
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L209" s="2" t="n"/>
-      <c r="M209" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/calendar", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="inlineStr"/>
+      <c r="M209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -14867,18 +13531,11 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L210" s="2" t="n"/>
-      <c r="M210" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/clarifications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -14936,18 +13593,11 @@
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L211" s="2" t="n"/>
-      <c r="M211" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/discussions", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="inlineStr"/>
+      <c r="M211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -15005,18 +13655,11 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L212" s="2" t="n"/>
-      <c r="M212" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L212" s="2" t="inlineStr"/>
+      <c r="M212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -15074,18 +13717,11 @@
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L213" s="2" t="n"/>
-      <c r="M213" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/employers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr"/>
+      <c r="M213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -15143,18 +13779,11 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L214" s="2" t="n"/>
-      <c r="M214" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/employers/requests", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr"/>
+      <c r="M214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -15212,18 +13841,11 @@
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L215" s="2" t="n"/>
-      <c r="M215" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/enrollment-key", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr"/>
+      <c r="M215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -15281,18 +13903,11 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L216" s="2" t="n"/>
-      <c r="M216" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/events", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L216" s="2" t="inlineStr"/>
+      <c r="M216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -15350,15 +13965,11 @@
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L217" s="2" t="n"/>
-      <c r="M217" s="2" t="inlineStr">
-        <is>
-          <t>User was able to access restricted route /dashboard/college/guest-engagements</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L217" s="2" t="inlineStr"/>
+      <c r="M217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -15416,18 +14027,11 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L218" s="2" t="n"/>
-      <c r="M218" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/hiring-assessment", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L218" s="2" t="inlineStr"/>
+      <c r="M218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -15485,18 +14089,11 @@
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L219" s="2" t="n"/>
-      <c r="M219" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/infrastructure", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L219" s="2" t="inlineStr"/>
+      <c r="M219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -15554,18 +14151,11 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L220" s="2" t="n"/>
-      <c r="M220" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/internship-results", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L220" s="2" t="inlineStr"/>
+      <c r="M220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -15623,18 +14213,11 @@
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L221" s="2" t="n"/>
-      <c r="M221" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/internships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L221" s="2" t="inlineStr"/>
+      <c r="M221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -15692,18 +14275,11 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L222" s="2" t="n"/>
-      <c r="M222" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/interviews", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L222" s="2" t="inlineStr"/>
+      <c r="M222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -15761,18 +14337,11 @@
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L223" s="2" t="n"/>
-      <c r="M223" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L223" s="2" t="inlineStr"/>
+      <c r="M223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -15830,18 +14399,11 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L224" s="2" t="n"/>
-      <c r="M224" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/offers-upload", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L224" s="2" t="inlineStr"/>
+      <c r="M224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -15899,18 +14461,11 @@
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L225" s="2" t="n"/>
-      <c r="M225" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L225" s="2" t="inlineStr"/>
+      <c r="M225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -15968,18 +14523,11 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L226" s="2" t="n"/>
-      <c r="M226" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/reports", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L226" s="2" t="inlineStr"/>
+      <c r="M226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -16037,18 +14585,11 @@
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L227" s="2" t="n"/>
-      <c r="M227" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/rules", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L227" s="2" t="inlineStr"/>
+      <c r="M227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -16106,18 +14647,11 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L228" s="2" t="n"/>
-      <c r="M228" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/settings", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L228" s="2" t="inlineStr"/>
+      <c r="M228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -16175,18 +14709,11 @@
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L229" s="2" t="n"/>
-      <c r="M229" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/sponsorships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L229" s="2" t="inlineStr"/>
+      <c r="M229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -16244,18 +14771,11 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L230" s="2" t="n"/>
-      <c r="M230" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/college/students", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L230" s="2" t="inlineStr"/>
+      <c r="M230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -16313,18 +14833,11 @@
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L231" s="2" t="n"/>
-      <c r="M231" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/applications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L231" s="2" t="inlineStr"/>
+      <c r="M231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -16382,18 +14895,11 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L232" s="2" t="n"/>
-      <c r="M232" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/assessment-summary", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L232" s="2" t="inlineStr"/>
+      <c r="M232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -16451,18 +14957,11 @@
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L233" s="2" t="n"/>
-      <c r="M233" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/assessment-uploads", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L233" s="2" t="inlineStr"/>
+      <c r="M233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -16520,18 +15019,11 @@
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L234" s="2" t="n"/>
-      <c r="M234" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/calendar", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L234" s="2" t="inlineStr"/>
+      <c r="M234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -16589,18 +15081,11 @@
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L235" s="2" t="n"/>
-      <c r="M235" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/campus-guest-needs", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L235" s="2" t="inlineStr"/>
+      <c r="M235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -16658,18 +15143,11 @@
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L236" s="2" t="n"/>
-      <c r="M236" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/discussions", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L236" s="2" t="inlineStr"/>
+      <c r="M236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -16727,18 +15205,11 @@
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L237" s="2" t="n"/>
-      <c r="M237" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L237" s="2" t="inlineStr"/>
+      <c r="M237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -16796,18 +15267,11 @@
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L238" s="2" t="n"/>
-      <c r="M238" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/hiring-assessment", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L238" s="2" t="inlineStr"/>
+      <c r="M238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -16865,18 +15329,11 @@
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L239" s="2" t="n"/>
-      <c r="M239" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/internships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L239" s="2" t="inlineStr"/>
+      <c r="M239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -16934,18 +15391,11 @@
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L240" s="2" t="n"/>
-      <c r="M240" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/interviews", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L240" s="2" t="inlineStr"/>
+      <c r="M240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -17003,18 +15453,11 @@
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L241" s="2" t="n"/>
-      <c r="M241" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/jobs", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="inlineStr"/>
+      <c r="M241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -17072,18 +15515,11 @@
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L242" s="2" t="n"/>
-      <c r="M242" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L242" s="2" t="inlineStr"/>
+      <c r="M242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -17141,18 +15577,11 @@
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L243" s="2" t="n"/>
-      <c r="M243" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/offers-upload", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L243" s="2" t="inlineStr"/>
+      <c r="M243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -17210,18 +15639,11 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L244" s="2" t="n"/>
-      <c r="M244" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L244" s="2" t="inlineStr"/>
+      <c r="M244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -17279,18 +15701,11 @@
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L245" s="2" t="n"/>
-      <c r="M245" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/profile", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="inlineStr"/>
+      <c r="M245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -17348,18 +15763,11 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L246" s="2" t="n"/>
-      <c r="M246" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/projects", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L246" s="2" t="inlineStr"/>
+      <c r="M246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -17417,18 +15825,11 @@
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L247" s="2" t="n"/>
-      <c r="M247" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/select-campus", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L247" s="2" t="inlineStr"/>
+      <c r="M247" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -17486,18 +15887,11 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L248" s="2" t="n"/>
-      <c r="M248" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/employer/sponsorships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L248" s="2" t="inlineStr"/>
+      <c r="M248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -17555,18 +15949,11 @@
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L249" s="2" t="n"/>
-      <c r="M249" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/feedback", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L249" s="2" t="inlineStr"/>
+      <c r="M249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -17624,18 +16011,11 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L250" s="2" t="n"/>
-      <c r="M250" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/applications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L250" s="2" t="inlineStr"/>
+      <c r="M250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -17693,18 +16073,11 @@
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L251" s="2" t="n"/>
-      <c r="M251" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/calendar", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L251" s="2" t="inlineStr"/>
+      <c r="M251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -17762,18 +16135,11 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L252" s="2" t="n"/>
-      <c r="M252" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/clarifications", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L252" s="2" t="inlineStr"/>
+      <c r="M252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -17831,18 +16197,11 @@
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L253" s="2" t="n"/>
-      <c r="M253" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/discussions", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L253" s="2" t="inlineStr"/>
+      <c r="M253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -17900,18 +16259,11 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L254" s="2" t="n"/>
-      <c r="M254" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/documents", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L254" s="2" t="inlineStr"/>
+      <c r="M254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -17969,18 +16321,11 @@
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L255" s="2" t="n"/>
-      <c r="M255" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/drives", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L255" s="2" t="inlineStr"/>
+      <c r="M255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -18038,18 +16383,11 @@
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L256" s="2" t="n"/>
-      <c r="M256" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/internships", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L256" s="2" t="inlineStr"/>
+      <c r="M256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -18107,18 +16445,11 @@
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L257" s="2" t="n"/>
-      <c r="M257" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/interviews", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L257" s="2" t="inlineStr"/>
+      <c r="M257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -18176,18 +16507,11 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L258" s="2" t="n"/>
-      <c r="M258" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/offers", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L258" s="2" t="inlineStr"/>
+      <c r="M258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -18245,18 +16569,11 @@
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L259" s="2" t="n"/>
-      <c r="M259" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/overview", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L259" s="2" t="inlineStr"/>
+      <c r="M259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -18314,18 +16631,11 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L260" s="2" t="n"/>
-      <c r="M260" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/profile", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L260" s="2" t="inlineStr"/>
+      <c r="M260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -18383,18 +16693,11 @@
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="L261" s="2" t="n"/>
-      <c r="M261" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page.goto: Timeout 8000ms exceeded.
-Call log:
-[2m  - navigating to "http://localhost:3000/dashboard/student/projects", waiting until "networkidle"[22m
-</t>
-        </is>
-      </c>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="L261" s="2" t="inlineStr"/>
+      <c r="M261" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
